--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.46243313838463</v>
+        <v>12.7501453849875</v>
       </c>
       <c r="D2" t="n">
-        <v>78.42359151089236</v>
+        <v>12.74383362052001</v>
       </c>
       <c r="E2" t="n">
-        <v>12.05730394902874</v>
+        <v>1.95931189171717</v>
       </c>
       <c r="F2" t="n">
-        <v>12.05874606653935</v>
+        <v>1.959546235812645</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>82.67677196238141</v>
+        <v>13.43497544388698</v>
       </c>
       <c r="D3" t="n">
-        <v>82.65000708986152</v>
+        <v>13.4306261521025</v>
       </c>
       <c r="E3" t="n">
-        <v>12.05730394902874</v>
+        <v>1.95931189171717</v>
       </c>
       <c r="F3" t="n">
-        <v>12.05874606653935</v>
+        <v>1.959546235812645</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.60399870321858</v>
+        <v>9.03564978927302</v>
       </c>
       <c r="D4" t="n">
-        <v>55.55306213606798</v>
+        <v>9.027372597111047</v>
       </c>
       <c r="E4" t="n">
-        <v>12.05730394902874</v>
+        <v>1.95931189171717</v>
       </c>
       <c r="F4" t="n">
-        <v>12.05874606653935</v>
+        <v>1.959546235812645</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.77416921490511</v>
+        <v>9.388302497422082</v>
       </c>
       <c r="D5" t="n">
-        <v>57.75909411087496</v>
+        <v>9.385852793017182</v>
       </c>
       <c r="E5" t="n">
-        <v>12.05730394902874</v>
+        <v>1.95931189171717</v>
       </c>
       <c r="F5" t="n">
-        <v>12.05874606653935</v>
+        <v>1.959546235812645</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
